--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -7615,10 +7615,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117851332</v>
+        <v>117851325</v>
       </c>
       <c r="B64" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7627,25 +7627,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496439</v>
+        <v>496367</v>
       </c>
       <c r="R64" t="n">
-        <v>6926600</v>
+        <v>6926792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7691,6 +7691,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7717,7 +7722,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117851325</v>
+        <v>117851328</v>
       </c>
       <c r="B65" t="n">
         <v>97836</v>
@@ -7757,10 +7762,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496367</v>
+        <v>496389</v>
       </c>
       <c r="R65" t="n">
-        <v>6926792</v>
+        <v>6926816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7797,7 +7802,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>41 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7824,10 +7829,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117851328</v>
+        <v>117851332</v>
       </c>
       <c r="B66" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,25 +7841,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7864,10 +7869,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496389</v>
+        <v>496439</v>
       </c>
       <c r="R66" t="n">
-        <v>6926816</v>
+        <v>6926600</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7900,11 +7905,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>41 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -6590,10 +6590,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117851319</v>
+        <v>117854657</v>
       </c>
       <c r="B54" t="n">
-        <v>79465</v>
+        <v>79561</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6602,25 +6602,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496348</v>
+        <v>496116</v>
       </c>
       <c r="R54" t="n">
-        <v>6926833</v>
+        <v>6926585</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6680,22 +6680,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117851334</v>
+        <v>117851319</v>
       </c>
       <c r="B55" t="n">
-        <v>91772</v>
+        <v>79465</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6708,21 +6708,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496097</v>
+        <v>496348</v>
       </c>
       <c r="R55" t="n">
-        <v>6926640</v>
+        <v>6926833</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117851337</v>
+        <v>117851318</v>
       </c>
       <c r="B56" t="n">
-        <v>91772</v>
+        <v>57303</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6806,25 +6806,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496456</v>
+        <v>496248</v>
       </c>
       <c r="R56" t="n">
-        <v>6926549</v>
+        <v>6926989</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6872,6 +6872,11 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6889,17 +6894,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117851327</v>
+        <v>117854659</v>
       </c>
       <c r="B57" t="n">
-        <v>97836</v>
+        <v>90648</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6912,21 +6917,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6936,10 +6941,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496388</v>
+        <v>496442</v>
       </c>
       <c r="R57" t="n">
-        <v>6926798</v>
+        <v>6926601</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6974,11 +6979,6 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>47 ex</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6991,22 +6991,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117854662</v>
+        <v>117854650</v>
       </c>
       <c r="B58" t="n">
-        <v>91772</v>
+        <v>90464</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7019,21 +7019,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496130</v>
+        <v>496248</v>
       </c>
       <c r="R58" t="n">
-        <v>6926356</v>
+        <v>6927002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7105,10 +7105,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117854650</v>
+        <v>117851332</v>
       </c>
       <c r="B59" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7117,25 +7117,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496248</v>
+        <v>496439</v>
       </c>
       <c r="R59" t="n">
-        <v>6927002</v>
+        <v>6926600</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7195,22 +7195,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117851320</v>
+        <v>117851338</v>
       </c>
       <c r="B60" t="n">
-        <v>5480</v>
+        <v>91772</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7219,25 +7219,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496105</v>
+        <v>496218</v>
       </c>
       <c r="R60" t="n">
-        <v>6926623</v>
+        <v>6927019</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7302,17 +7302,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Marielle Löthman, Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117851316</v>
+        <v>117851336</v>
       </c>
       <c r="B61" t="n">
-        <v>79098</v>
+        <v>91772</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7321,25 +7321,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496164</v>
+        <v>496361</v>
       </c>
       <c r="R61" t="n">
-        <v>6926332</v>
+        <v>6926238</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117854652</v>
+        <v>117854662</v>
       </c>
       <c r="B62" t="n">
-        <v>91962</v>
+        <v>91772</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7423,25 +7423,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496154</v>
+        <v>496130</v>
       </c>
       <c r="R62" t="n">
-        <v>6926416</v>
+        <v>6926356</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117851333</v>
+        <v>117851316</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7529,21 +7529,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496383</v>
+        <v>496164</v>
       </c>
       <c r="R63" t="n">
-        <v>6926731</v>
+        <v>6926332</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7615,10 +7615,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117851325</v>
+        <v>117851331</v>
       </c>
       <c r="B64" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7627,25 +7627,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496367</v>
+        <v>496508</v>
       </c>
       <c r="R64" t="n">
-        <v>6926792</v>
+        <v>6926456</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7691,11 +7691,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7722,10 +7717,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117851328</v>
+        <v>117851321</v>
       </c>
       <c r="B65" t="n">
-        <v>97836</v>
+        <v>78506</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7734,25 +7729,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7762,10 +7757,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496389</v>
+        <v>496245</v>
       </c>
       <c r="R65" t="n">
-        <v>6926816</v>
+        <v>6926998</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7798,11 +7793,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>41 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7829,10 +7819,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117851332</v>
+        <v>117851322</v>
       </c>
       <c r="B66" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7845,21 +7835,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7869,10 +7859,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496439</v>
+        <v>496355</v>
       </c>
       <c r="R66" t="n">
-        <v>6926600</v>
+        <v>6926903</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7931,10 +7921,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117854654</v>
+        <v>117851334</v>
       </c>
       <c r="B67" t="n">
-        <v>91962</v>
+        <v>91772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7943,25 +7933,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7971,10 +7961,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496327</v>
+        <v>496097</v>
       </c>
       <c r="R67" t="n">
-        <v>6926909</v>
+        <v>6926640</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8021,22 +8011,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117851318</v>
+        <v>117854661</v>
       </c>
       <c r="B68" t="n">
-        <v>57303</v>
+        <v>90743</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8045,25 +8035,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8073,10 +8063,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496248</v>
+        <v>496235</v>
       </c>
       <c r="R68" t="n">
-        <v>6926989</v>
+        <v>6927007</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8111,11 +8101,6 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8128,22 +8113,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117851335</v>
+        <v>117851324</v>
       </c>
       <c r="B69" t="n">
-        <v>91772</v>
+        <v>78216</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8152,25 +8137,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8180,10 +8165,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496131</v>
+        <v>496355</v>
       </c>
       <c r="R69" t="n">
-        <v>6926325</v>
+        <v>6926903</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8242,10 +8227,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117851338</v>
+        <v>117851328</v>
       </c>
       <c r="B70" t="n">
-        <v>91772</v>
+        <v>97836</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8254,25 +8239,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8282,10 +8267,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496218</v>
+        <v>496389</v>
       </c>
       <c r="R70" t="n">
-        <v>6927019</v>
+        <v>6926816</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8320,6 +8305,11 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>41 ex</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8337,14 +8327,14 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Linda Spjut, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117851336</v>
+        <v>117851335</v>
       </c>
       <c r="B71" t="n">
         <v>91772</v>
@@ -8384,10 +8374,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496361</v>
+        <v>496131</v>
       </c>
       <c r="R71" t="n">
-        <v>6926238</v>
+        <v>6926325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8446,10 +8436,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117851331</v>
+        <v>117851320</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>5480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8462,21 +8452,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>101410</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8486,10 +8476,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496508</v>
+        <v>496105</v>
       </c>
       <c r="R72" t="n">
-        <v>6926456</v>
+        <v>6926623</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8548,10 +8538,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117854661</v>
+        <v>117854655</v>
       </c>
       <c r="B73" t="n">
-        <v>90743</v>
+        <v>91962</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8560,25 +8550,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8591,7 +8581,7 @@
         <v>496235</v>
       </c>
       <c r="R73" t="n">
-        <v>6927007</v>
+        <v>6927006</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8650,10 +8640,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117851322</v>
+        <v>117851337</v>
       </c>
       <c r="B74" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8662,25 +8652,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8690,10 +8680,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496355</v>
+        <v>496456</v>
       </c>
       <c r="R74" t="n">
-        <v>6926903</v>
+        <v>6926549</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8745,17 +8735,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Marielle Löthman, Linda Spjut, Amanda Tas</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117851321</v>
+        <v>117854660</v>
       </c>
       <c r="B75" t="n">
-        <v>78506</v>
+        <v>78480</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8764,25 +8754,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8792,10 +8782,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496245</v>
+        <v>496496</v>
       </c>
       <c r="R75" t="n">
-        <v>6926998</v>
+        <v>6926411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8842,22 +8832,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117851324</v>
+        <v>117851333</v>
       </c>
       <c r="B76" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8870,21 +8860,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8894,10 +8884,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496355</v>
+        <v>496383</v>
       </c>
       <c r="R76" t="n">
-        <v>6926903</v>
+        <v>6926731</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8956,10 +8946,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117854653</v>
+        <v>117851327</v>
       </c>
       <c r="B77" t="n">
-        <v>91962</v>
+        <v>97836</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8968,25 +8958,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8996,10 +8986,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496446</v>
+        <v>496388</v>
       </c>
       <c r="R77" t="n">
-        <v>6926607</v>
+        <v>6926798</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9034,6 +9024,11 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>47 ex</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9046,22 +9041,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117851326</v>
+        <v>117854653</v>
       </c>
       <c r="B78" t="n">
-        <v>97836</v>
+        <v>91962</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9070,25 +9065,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9098,10 +9093,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496501</v>
+        <v>496446</v>
       </c>
       <c r="R78" t="n">
-        <v>6926441</v>
+        <v>6926607</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9136,11 +9131,6 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>36 ex</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9153,22 +9143,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117854657</v>
+        <v>117851326</v>
       </c>
       <c r="B79" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9177,25 +9167,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9205,10 +9195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496116</v>
+        <v>496501</v>
       </c>
       <c r="R79" t="n">
-        <v>6926585</v>
+        <v>6926441</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9243,6 +9233,11 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>36 ex</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9255,22 +9250,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117854660</v>
+        <v>117854652</v>
       </c>
       <c r="B80" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9283,21 +9278,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9307,10 +9302,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496496</v>
+        <v>496154</v>
       </c>
       <c r="R80" t="n">
-        <v>6926411</v>
+        <v>6926416</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9369,10 +9364,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117854659</v>
+        <v>117851325</v>
       </c>
       <c r="B81" t="n">
-        <v>90648</v>
+        <v>97836</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9385,21 +9380,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9409,10 +9404,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496442</v>
+        <v>496367</v>
       </c>
       <c r="R81" t="n">
-        <v>6926601</v>
+        <v>6926792</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9447,6 +9442,11 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>40 ex</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9459,19 +9459,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117854655</v>
+        <v>117854654</v>
       </c>
       <c r="B82" t="n">
         <v>91962</v>
@@ -9511,10 +9511,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496235</v>
+        <v>496327</v>
       </c>
       <c r="R82" t="n">
-        <v>6927006</v>
+        <v>6926909</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -6481,7 +6481,7 @@
         <v>117837632</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6590,10 +6590,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117854657</v>
+        <v>117854650</v>
       </c>
       <c r="B54" t="n">
-        <v>79561</v>
+        <v>90466</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6602,25 +6602,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496116</v>
+        <v>496248</v>
       </c>
       <c r="R54" t="n">
-        <v>6926585</v>
+        <v>6927002</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117851319</v>
+        <v>117851321</v>
       </c>
       <c r="B55" t="n">
-        <v>79465</v>
+        <v>78508</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6708,21 +6708,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496348</v>
+        <v>496245</v>
       </c>
       <c r="R55" t="n">
-        <v>6926833</v>
+        <v>6926998</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117851318</v>
+        <v>117851328</v>
       </c>
       <c r="B56" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6806,25 +6806,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496248</v>
+        <v>496389</v>
       </c>
       <c r="R56" t="n">
-        <v>6926989</v>
+        <v>6926816</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>41 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6901,10 +6901,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117854659</v>
+        <v>117851320</v>
       </c>
       <c r="B57" t="n">
-        <v>90648</v>
+        <v>5480</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6913,25 +6913,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>101410</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496442</v>
+        <v>496105</v>
       </c>
       <c r="R57" t="n">
-        <v>6926601</v>
+        <v>6926623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6991,22 +6991,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117854650</v>
+        <v>117851318</v>
       </c>
       <c r="B58" t="n">
-        <v>90464</v>
+        <v>57304</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7015,25 +7015,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
         <v>496248</v>
       </c>
       <c r="R58" t="n">
-        <v>6927002</v>
+        <v>6926989</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7081,6 +7081,11 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7093,22 +7098,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117851332</v>
+        <v>117854662</v>
       </c>
       <c r="B59" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7117,25 +7122,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7145,10 +7150,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496439</v>
+        <v>496130</v>
       </c>
       <c r="R59" t="n">
-        <v>6926600</v>
+        <v>6926356</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7195,22 +7200,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117851338</v>
+        <v>117851337</v>
       </c>
       <c r="B60" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7247,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496218</v>
+        <v>496456</v>
       </c>
       <c r="R60" t="n">
-        <v>6927019</v>
+        <v>6926549</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7309,10 +7314,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117851336</v>
+        <v>117851333</v>
       </c>
       <c r="B61" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7321,25 +7326,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7349,10 +7354,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496361</v>
+        <v>496383</v>
       </c>
       <c r="R61" t="n">
-        <v>6926238</v>
+        <v>6926731</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7411,10 +7416,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117854662</v>
+        <v>117851316</v>
       </c>
       <c r="B62" t="n">
-        <v>91772</v>
+        <v>79100</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7423,25 +7428,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7451,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496130</v>
+        <v>496164</v>
       </c>
       <c r="R62" t="n">
-        <v>6926356</v>
+        <v>6926332</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7501,22 +7506,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117851316</v>
+        <v>117854654</v>
       </c>
       <c r="B63" t="n">
-        <v>79098</v>
+        <v>91964</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7529,21 +7534,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7553,10 +7558,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496164</v>
+        <v>496327</v>
       </c>
       <c r="R63" t="n">
-        <v>6926332</v>
+        <v>6926909</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7603,22 +7608,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117851331</v>
+        <v>117851334</v>
       </c>
       <c r="B64" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7627,25 +7632,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7655,10 +7660,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496508</v>
+        <v>496097</v>
       </c>
       <c r="R64" t="n">
-        <v>6926456</v>
+        <v>6926640</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7717,10 +7722,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117851321</v>
+        <v>117851324</v>
       </c>
       <c r="B65" t="n">
-        <v>78506</v>
+        <v>78218</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7729,25 +7734,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7757,10 +7762,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496245</v>
+        <v>496355</v>
       </c>
       <c r="R65" t="n">
-        <v>6926998</v>
+        <v>6926903</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7819,10 +7824,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117851322</v>
+        <v>117851325</v>
       </c>
       <c r="B66" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7831,25 +7836,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7859,10 +7864,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496355</v>
+        <v>496367</v>
       </c>
       <c r="R66" t="n">
-        <v>6926903</v>
+        <v>6926792</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7895,6 +7900,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7921,10 +7931,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117851334</v>
+        <v>117851327</v>
       </c>
       <c r="B67" t="n">
-        <v>91772</v>
+        <v>97838</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7933,25 +7943,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7961,10 +7971,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496097</v>
+        <v>496388</v>
       </c>
       <c r="R67" t="n">
-        <v>6926640</v>
+        <v>6926798</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7997,6 +8007,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>47 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8023,10 +8038,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117854661</v>
+        <v>117854655</v>
       </c>
       <c r="B68" t="n">
-        <v>90743</v>
+        <v>91964</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8035,25 +8050,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8066,7 +8081,7 @@
         <v>496235</v>
       </c>
       <c r="R68" t="n">
-        <v>6927007</v>
+        <v>6927006</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8118,17 +8133,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117851324</v>
+        <v>117854652</v>
       </c>
       <c r="B69" t="n">
-        <v>78216</v>
+        <v>91964</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8141,21 +8156,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8165,10 +8180,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496355</v>
+        <v>496154</v>
       </c>
       <c r="R69" t="n">
-        <v>6926903</v>
+        <v>6926416</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8215,22 +8230,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117851328</v>
+        <v>117851319</v>
       </c>
       <c r="B70" t="n">
-        <v>97836</v>
+        <v>79467</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8239,25 +8254,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8267,10 +8282,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496389</v>
+        <v>496348</v>
       </c>
       <c r="R70" t="n">
-        <v>6926816</v>
+        <v>6926833</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8303,11 +8318,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>41 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8334,10 +8344,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117851335</v>
+        <v>117851331</v>
       </c>
       <c r="B71" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8346,25 +8356,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8374,10 +8384,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496131</v>
+        <v>496508</v>
       </c>
       <c r="R71" t="n">
-        <v>6926325</v>
+        <v>6926456</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8436,10 +8446,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117851320</v>
+        <v>117851336</v>
       </c>
       <c r="B72" t="n">
-        <v>5480</v>
+        <v>91774</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8448,25 +8458,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8476,10 +8486,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496105</v>
+        <v>496361</v>
       </c>
       <c r="R72" t="n">
-        <v>6926623</v>
+        <v>6926238</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8538,10 +8548,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117854655</v>
+        <v>117854659</v>
       </c>
       <c r="B73" t="n">
-        <v>91962</v>
+        <v>90650</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8550,25 +8560,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8578,10 +8588,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496235</v>
+        <v>496442</v>
       </c>
       <c r="R73" t="n">
-        <v>6927006</v>
+        <v>6926601</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8633,17 +8643,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117851337</v>
+        <v>117851338</v>
       </c>
       <c r="B74" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8680,10 +8690,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496456</v>
+        <v>496218</v>
       </c>
       <c r="R74" t="n">
-        <v>6926549</v>
+        <v>6927019</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8742,10 +8752,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117854660</v>
+        <v>117854661</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>90745</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8754,25 +8764,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8782,10 +8792,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496496</v>
+        <v>496235</v>
       </c>
       <c r="R75" t="n">
-        <v>6926411</v>
+        <v>6927007</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8837,17 +8847,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117851333</v>
+        <v>117851335</v>
       </c>
       <c r="B76" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8856,25 +8866,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8884,10 +8894,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496383</v>
+        <v>496131</v>
       </c>
       <c r="R76" t="n">
-        <v>6926731</v>
+        <v>6926325</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8946,10 +8956,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117851327</v>
+        <v>117854653</v>
       </c>
       <c r="B77" t="n">
-        <v>97836</v>
+        <v>91964</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8958,25 +8968,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8986,10 +8996,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496388</v>
+        <v>496446</v>
       </c>
       <c r="R77" t="n">
-        <v>6926798</v>
+        <v>6926607</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9024,11 +9034,6 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>47 ex</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9041,22 +9046,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117854653</v>
+        <v>117851332</v>
       </c>
       <c r="B78" t="n">
-        <v>91962</v>
+        <v>78482</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9069,21 +9074,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9093,10 +9098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496446</v>
+        <v>496439</v>
       </c>
       <c r="R78" t="n">
-        <v>6926607</v>
+        <v>6926600</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9143,22 +9148,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117851326</v>
+        <v>117854657</v>
       </c>
       <c r="B79" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9167,25 +9172,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9195,10 +9200,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496501</v>
+        <v>496116</v>
       </c>
       <c r="R79" t="n">
-        <v>6926441</v>
+        <v>6926585</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9233,11 +9238,6 @@
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>36 ex</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9250,22 +9250,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117854652</v>
+        <v>117854660</v>
       </c>
       <c r="B80" t="n">
-        <v>91962</v>
+        <v>78482</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9278,21 +9278,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9302,10 +9302,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496154</v>
+        <v>496496</v>
       </c>
       <c r="R80" t="n">
-        <v>6926416</v>
+        <v>6926411</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9357,17 +9357,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117851325</v>
+        <v>117851326</v>
       </c>
       <c r="B81" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496367</v>
+        <v>496501</v>
       </c>
       <c r="R81" t="n">
-        <v>6926792</v>
+        <v>6926441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9471,10 +9471,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117854654</v>
+        <v>117851322</v>
       </c>
       <c r="B82" t="n">
-        <v>91962</v>
+        <v>78219</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9487,21 +9487,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9511,10 +9511,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496327</v>
+        <v>496355</v>
       </c>
       <c r="R82" t="n">
-        <v>6926909</v>
+        <v>6926903</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9561,12 +9561,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Amanda Tas, Linda Spjut, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -3516,7 +3516,7 @@
         <v>116318006</v>
       </c>
       <c r="B27" t="n">
-        <v>57277</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gillberget  (Gillberget ), Jmt</t>
+          <t>Gillberget , Gillberget , Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -3516,7 +3516,7 @@
         <v>116318006</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -3516,7 +3516,7 @@
         <v>116318006</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -1590,12 +1590,7 @@
         <v>116256184</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,7 +1618,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gillberget  (Gillberget ), Jmt</t>
+          <t>Gillberget , Gillberget , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -7210,12 +7205,7 @@
         <v>117851318</v>
       </c>
       <c r="B60" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -1590,7 +1590,7 @@
         <v>116256184</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>117851318</v>
       </c>
       <c r="B60" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -1590,7 +1590,7 @@
         <v>116256184</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>117851318</v>
       </c>
       <c r="B60" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -1590,7 +1590,7 @@
         <v>116256184</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>117851318</v>
       </c>
       <c r="B60" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -1590,7 +1590,7 @@
         <v>116256184</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>117851318</v>
       </c>
       <c r="B60" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -1590,7 +1590,7 @@
         <v>116256184</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>117851318</v>
       </c>
       <c r="B60" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 44245-2021 artfynd.xlsx
+++ b/artfynd/A 44245-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854661</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116316013</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116256396</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257739</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854659</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854654</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854655</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1676,6 +1726,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111281287</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255635</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257337</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116325632</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116325771</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116327273</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851334</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851335</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851336</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851337</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2696,6 +2796,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851338</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854662</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111281235</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3002,6 +3117,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116326635</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854650</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3206,6 +3331,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116254604</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3313,6 +3443,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116316294</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3420,6 +3555,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116316667</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116322996</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3624,6 +3769,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851331</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3721,6 +3871,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851332</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3818,6 +3973,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851333</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3915,6 +4075,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854660</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4012,6 +4177,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851321</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4114,6 +4284,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111281261</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4221,6 +4396,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116254644</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4328,6 +4508,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255650</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4435,6 +4620,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116320724</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116327663</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4639,6 +4834,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851324</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4741,6 +4941,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111281238</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4838,6 +5043,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851316</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4935,6 +5145,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851317</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5032,6 +5247,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854651</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5129,6 +5349,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851319</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5241,6 +5466,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102136310</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5353,6 +5583,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102137210</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5461,6 +5696,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111536627</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5568,6 +5808,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116256925</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5675,6 +5920,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116327469</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5772,6 +6022,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854657</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5879,6 +6134,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116325233</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5986,6 +6246,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116256184</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6088,6 +6353,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851318</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6208,6 +6478,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116318006</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6326,6 +6601,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102136845</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6438,6 +6718,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116318260</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6550,6 +6835,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116324557</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6647,6 +6937,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851320</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6754,6 +7049,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257901</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6859,6 +7159,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116637192</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6974,6 +7279,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116318347</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7095,6 +7405,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116256471</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7211,6 +7526,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116258119</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7322,6 +7642,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116321289</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7429,6 +7754,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116322958</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7540,6 +7870,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116323113</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7651,6 +7986,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116323224</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7758,6 +8098,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116323432</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7869,6 +8214,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116323491</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7980,6 +8330,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116324035</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8091,6 +8446,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116324157</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8202,6 +8562,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116326203</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8309,6 +8674,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117837632</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8411,6 +8781,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851325</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8513,6 +8888,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851326</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8615,6 +8995,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851327</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8717,6 +9102,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851328</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8819,6 +9209,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851329</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8932,6 +9327,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102136169</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9034,6 +9434,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111281249</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9141,6 +9546,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116254649</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9248,6 +9658,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255647</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9355,6 +9770,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255690</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9462,6 +9882,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255884</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9569,6 +9994,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116256082</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9676,6 +10106,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116258366</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9783,6 +10218,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116317394</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9890,6 +10330,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116318828</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9997,6 +10442,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116327019</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10094,6 +10544,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851322</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10191,6 +10646,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117851323</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10288,6 +10748,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117854656</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10395,6 +10860,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116254695</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10502,6 +10972,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255228</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10609,8 +11084,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116315903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>